--- a/ONCHO/Impact Assessments/Nigeria/2025/river states ia/sites.xlsx
+++ b/ONCHO/Impact Assessments/Nigeria/2025/river states ia/sites.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Nigeria\2025\river states\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Nigeria\2025\river states ia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E6B291-F3AB-4C8B-BAEE-E61E9EB2BD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CE9775-527B-4470-B0C9-EB4ED015DBC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="impact Assessment" sheetId="1" r:id="rId1"/>
@@ -925,10 +925,10 @@
       <c r="E4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="J4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" t="s">
         <v>68</v>
       </c>
       <c r="M4" s="2" t="s">
@@ -1047,10 +1047,10 @@
       <c r="K8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="2" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1058,16 +1058,16 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>134</v>
       </c>
       <c r="J9" s="2" t="s">
@@ -1076,10 +1076,10 @@
       <c r="K9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="2" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1087,16 +1087,16 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>135</v>
       </c>
       <c r="J10" s="2" t="s">
@@ -1116,16 +1116,16 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>136</v>
       </c>
       <c r="J11" s="2" t="s">
@@ -1134,10 +1134,10 @@
       <c r="K11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="2" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>85</v>
       </c>
       <c r="J12" s="2" t="s">
@@ -1174,16 +1174,16 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" t="s">
         <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" t="s">
         <v>86</v>
       </c>
       <c r="J13" s="2" t="s">
@@ -1203,22 +1203,22 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" t="s">
         <v>87</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" t="s">
         <v>68</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1238,10 +1238,10 @@
       <c r="E15" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="M15" t="s">
         <v>68</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N15" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1261,10 +1261,10 @@
       <c r="E16" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" t="s">
         <v>68</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1537,10 +1537,10 @@
       <c r="E28" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M28" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="N28" t="s">
+      <c r="N28" s="2" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1571,22 +1571,22 @@
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="M30" t="s">
+      <c r="M30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="N30" t="s">
+      <c r="N30" s="2" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1594,16 +1594,16 @@
       <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="2" t="s">
         <v>133</v>
       </c>
       <c r="M31" s="2" t="s">
@@ -1652,10 +1652,10 @@
       <c r="E33" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="M33" t="s">
         <v>72</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="N33" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1686,22 +1686,22 @@
       <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="B35" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" t="s">
         <v>72</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" t="s">
         <v>105</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="M35" t="s">
         <v>72</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="N35" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1709,16 +1709,16 @@
       <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="B36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" t="s">
         <v>72</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" t="s">
         <v>106</v>
       </c>
       <c r="M36" s="2" t="s">
